--- a/docs/samples/kuaima-verified-standard/满减/standard_preview.xlsx
+++ b/docs/samples/kuaima-verified-standard/满减/standard_preview.xlsx
@@ -6226,7 +6226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6318,6 +6318,41 @@
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>已结束</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>KM-COUPON-AUTO-001</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>test1</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>满一定金额立减</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr"/>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-09 16:50:00</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 16:50:00</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr"/>
+      <c r="H3" s="1" t="inlineStr"/>
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>已结束</t>
         </is>
@@ -6334,7 +6369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6396,6 +6431,38 @@
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>KM-COUPON-AUTO-001</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>0</t>
         </is>
